--- a/data/trans_orig/IMC_inf_MED_R2-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Dificultad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>95358</v>
+        <v>114849</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>84804</v>
+        <v>102691</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>105632</v>
+        <v>126284</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5485985152616594</v>
+        <v>0.5394513918839032</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4878809449007006</v>
+        <v>0.4823418331700404</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6077014241975511</v>
+        <v>0.5931628788391202</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>80880</v>
+        <v>97409</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>70383</v>
+        <v>84830</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>91213</v>
+        <v>108753</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4866308558102792</v>
+        <v>0.485901205573558</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.4234741167300994</v>
+        <v>0.4231579704037719</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5488027659627774</v>
+        <v>0.5424878798962334</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>176238</v>
+        <v>212258</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>160959</v>
+        <v>196307</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>190688</v>
+        <v>230187</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5183088455425006</v>
+        <v>0.513481465838745</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4733738435805489</v>
+        <v>0.4748941355304176</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5608044828143383</v>
+        <v>0.5568549420483124</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>78464</v>
+        <v>98051</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>68190</v>
+        <v>86616</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>89018</v>
+        <v>110209</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4514014847383406</v>
+        <v>0.4605486081160968</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3922985758024489</v>
+        <v>0.4068371211608797</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5121190550992994</v>
+        <v>0.5176581668299596</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>85324</v>
+        <v>103061</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>74991</v>
+        <v>91717</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>95821</v>
+        <v>115640</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5133691441897209</v>
+        <v>0.514098794426442</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4511972340372224</v>
+        <v>0.4575121201037666</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5765258832699004</v>
+        <v>0.5768420295962282</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>163787</v>
+        <v>201112</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>149337</v>
+        <v>183183</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>179066</v>
+        <v>217063</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4816911544574994</v>
+        <v>0.4865185341612551</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4391955171856617</v>
+        <v>0.4431450579516872</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5266261564194511</v>
+        <v>0.5251058644695822</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>173822</v>
+        <v>212900</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>166204</v>
+        <v>200470</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>492</v>
+        <v>594</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>340025</v>
+        <v>413370</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>94035</v>
+        <v>100279</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>84176</v>
+        <v>89279</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>104520</v>
+        <v>110863</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5799651498898299</v>
+        <v>0.5495807751474314</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.5191572800104644</v>
+        <v>0.4892962631790516</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6446298346245768</v>
+        <v>0.6075870884891789</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>68115</v>
+        <v>77500</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>57589</v>
+        <v>66150</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>78635</v>
+        <v>87409</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.443025755971494</v>
+        <v>0.4318603798107185</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3745672028353506</v>
+        <v>0.3686142223512505</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5114479501347368</v>
+        <v>0.4870830280401883</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>162150</v>
+        <v>177778</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>147295</v>
+        <v>162197</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>176459</v>
+        <v>193598</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5133140141494416</v>
+        <v>0.4912099463844857</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4662862416687281</v>
+        <v>0.4481587129007674</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5586098525300687</v>
+        <v>0.5349234590043802</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>68104</v>
+        <v>82185</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>57619</v>
+        <v>71601</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>77963</v>
+        <v>93185</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4200348501101701</v>
+        <v>0.4504192248525686</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3553701653754231</v>
+        <v>0.3924129115108211</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.4808427199895356</v>
+        <v>0.5107037368209484</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>85634</v>
+        <v>101955</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>75114</v>
+        <v>92046</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>96160</v>
+        <v>113305</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.556974244028506</v>
+        <v>0.5681396201892815</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4885520498652632</v>
+        <v>0.5129169719598119</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6254327971646495</v>
+        <v>0.63138577764875</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>153739</v>
+        <v>184140</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>139430</v>
+        <v>168320</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>168594</v>
+        <v>199721</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.4866859858505585</v>
+        <v>0.5087900536155143</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4413901474699314</v>
+        <v>0.4650765409956198</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.533713758331272</v>
+        <v>0.5518412870992327</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>162139</v>
+        <v>182464</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>153749</v>
+        <v>179455</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>450</v>
+        <v>517</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>315889</v>
+        <v>361918</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>51914</v>
+        <v>62508</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>43632</v>
+        <v>52703</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60362</v>
+        <v>71539</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4860180086282767</v>
+        <v>0.4615316026568044</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4084830562336539</v>
+        <v>0.3891350748329719</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5651068144927311</v>
+        <v>0.5282092706288272</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>41108</v>
+        <v>51669</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>33338</v>
+        <v>42211</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>50320</v>
+        <v>60360</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3819214476362632</v>
+        <v>0.3898486877322933</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3097319748095254</v>
+        <v>0.3184869569120726</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4675083254724131</v>
+        <v>0.4554237368143803</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>93022</v>
+        <v>114177</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>81672</v>
+        <v>100955</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>105618</v>
+        <v>127559</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.4337710316329528</v>
+        <v>0.4260783476213989</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3808444959501786</v>
+        <v>0.3767375774828189</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4925100430534096</v>
+        <v>0.4760178927471927</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>54901</v>
+        <v>72929</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>46453</v>
+        <v>63898</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>63183</v>
+        <v>82734</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5139819913717233</v>
+        <v>0.5384683973431956</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4348931855072686</v>
+        <v>0.4717907293711726</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.591516943766345</v>
+        <v>0.6108649251670281</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>66526</v>
+        <v>80866</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>57314</v>
+        <v>72175</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>74296</v>
+        <v>90324</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6180785523637368</v>
+        <v>0.6101513122677068</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5324916745275871</v>
+        <v>0.5445762631856197</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6902680251904747</v>
+        <v>0.6815130430879274</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>121427</v>
+        <v>153795</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>108831</v>
+        <v>140413</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>132777</v>
+        <v>167017</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.5662289683670473</v>
+        <v>0.573921652378601</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5074899569465903</v>
+        <v>0.5239821072528072</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6191555040498213</v>
+        <v>0.6232624225171809</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>106815</v>
+        <v>135437</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>107634</v>
+        <v>132535</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>214449</v>
+        <v>267972</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>29540</v>
+        <v>36662</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>22887</v>
+        <v>29503</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>35963</v>
+        <v>44838</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4559556889530917</v>
+        <v>0.4777044104511418</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.353270704816191</v>
+        <v>0.3844241291560295</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5550980701712727</v>
+        <v>0.5842324752201639</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>28772</v>
+        <v>33201</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>22153</v>
+        <v>26562</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>34736</v>
+        <v>40026</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.483706411545652</v>
+        <v>0.4942971057060551</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3724284537940025</v>
+        <v>0.3954503529967355</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5839763165506984</v>
+        <v>0.5959021790713257</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>58312</v>
+        <v>69863</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>48533</v>
+        <v>59015</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>67235</v>
+        <v>79344</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4692388389836714</v>
+        <v>0.485448533465914</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3905496375167692</v>
+        <v>0.4100675924257361</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5410458226903844</v>
+        <v>0.551327244785368</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>35246</v>
+        <v>40085</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>28823</v>
+        <v>31909</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>41899</v>
+        <v>47244</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5440443110469082</v>
+        <v>0.5222955895488582</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4449019298287273</v>
+        <v>0.4157675247798364</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6467292951838091</v>
+        <v>0.6155758708439706</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>30710</v>
+        <v>33967</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>24746</v>
+        <v>27142</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>37329</v>
+        <v>40606</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.516293588454348</v>
+        <v>0.5057028942939449</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4160236834493022</v>
+        <v>0.4040978209286742</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6275715462059975</v>
+        <v>0.6045496470032644</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>65957</v>
+        <v>74052</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>57034</v>
+        <v>64571</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>75736</v>
+        <v>84900</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5307611610163286</v>
+        <v>0.514551466534086</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4589541773096157</v>
+        <v>0.4486727552146319</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6094503624832308</v>
+        <v>0.5899324075742639</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>64786</v>
+        <v>76747</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>59482</v>
+        <v>67168</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>124269</v>
+        <v>143915</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>270847</v>
+        <v>314299</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>251340</v>
+        <v>292906</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>289093</v>
+        <v>333769</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.5336234893388987</v>
+        <v>0.5173232725418957</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.495190029589317</v>
+        <v>0.4821123133352459</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5695726695894925</v>
+        <v>0.5493711048680652</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>218874</v>
+        <v>259777</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>201621</v>
+        <v>238898</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>237299</v>
+        <v>278787</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4493702869290529</v>
+        <v>0.4481799647969205</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.413947317264619</v>
+        <v>0.4121578325308833</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4871982796117309</v>
+        <v>0.4809760134795105</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>700</v>
+        <v>816</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>489721</v>
+        <v>574076</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>463409</v>
+        <v>547562</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>513979</v>
+        <v>601369</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4923648546905175</v>
+        <v>0.4835647167147402</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.4659105339311578</v>
+        <v>0.4612310662471268</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5167530499710475</v>
+        <v>0.5065547285028233</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>236715</v>
+        <v>293249</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>218469</v>
+        <v>273779</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>256222</v>
+        <v>314642</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4663765106611013</v>
+        <v>0.4826767274581043</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4304273304105075</v>
+        <v>0.4506288951319348</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.504809970410683</v>
+        <v>0.517887686664754</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>386</v>
+        <v>460</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>268195</v>
+        <v>319850</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>249770</v>
+        <v>300840</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>285448</v>
+        <v>340729</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5506297130709471</v>
+        <v>0.5518200352030794</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5128017203882691</v>
+        <v>0.5190239865204895</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.586052682735381</v>
+        <v>0.5878421674691164</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>727</v>
+        <v>883</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>504910</v>
+        <v>613099</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>480652</v>
+        <v>585806</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>531222</v>
+        <v>639613</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5076351453094825</v>
+        <v>0.5164352832852598</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4832469500289523</v>
+        <v>0.4934452714971767</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.5340894660688421</v>
+        <v>0.5387689337528732</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>729</v>
+        <v>869</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>507562</v>
+        <v>607548</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>698</v>
+        <v>830</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487069</v>
+        <v>579627</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1427</v>
+        <v>1699</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>994631</v>
+        <v>1187175</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>95495</v>
+        <v>115019</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>84669</v>
+        <v>101527</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>107739</v>
+        <v>127852</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.4808004291001908</v>
+        <v>0.466919426301532</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4262939637856952</v>
+        <v>0.4121502406809524</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.5424441188675454</v>
+        <v>0.5190130768475942</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>64741</v>
+        <v>76428</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>55333</v>
+        <v>66977</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>75946</v>
+        <v>89417</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3635498056915927</v>
+        <v>0.3522354480577291</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.310721296280061</v>
+        <v>0.3086784015498192</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.426473636179685</v>
+        <v>0.4120938407942307</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>160236</v>
+        <v>191447</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>146203</v>
+        <v>172848</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>176674</v>
+        <v>209280</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4253714772376245</v>
+        <v>0.413210461130649</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3881193159495689</v>
+        <v>0.3730669840683027</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.4690090968295675</v>
+        <v>0.4516992853522911</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>103122</v>
+        <v>131317</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>90878</v>
+        <v>118484</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>113948</v>
+        <v>144809</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5191995708998093</v>
+        <v>0.533080573698468</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4575558811324545</v>
+        <v>0.4809869231524059</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5737060362143048</v>
+        <v>0.5878497593190478</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>113338</v>
+        <v>140553</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>102133</v>
+        <v>127564</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>122746</v>
+        <v>150004</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6364501943084073</v>
+        <v>0.6477645519422709</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.573526363820315</v>
+        <v>0.5879061592057694</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.689278703719939</v>
+        <v>0.691321598450181</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>216460</v>
+        <v>271870</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>200022</v>
+        <v>254037</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>230493</v>
+        <v>290469</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5746285227623755</v>
+        <v>0.5867895388693509</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.5309909031704324</v>
+        <v>0.5483007146477089</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6118806840504312</v>
+        <v>0.6269330159316973</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>198617</v>
+        <v>246336</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>178079</v>
+        <v>216981</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>550</v>
+        <v>675</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>376696</v>
+        <v>463317</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>62930</v>
+        <v>74127</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>53309</v>
+        <v>63431</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>72326</v>
+        <v>84308</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4210536408878094</v>
+        <v>0.4361931027382643</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3566772236050965</v>
+        <v>0.3732581228575776</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.4839171267309413</v>
+        <v>0.4961057049156432</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>50650</v>
+        <v>57453</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>42288</v>
+        <v>47854</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>60657</v>
+        <v>68371</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.348925956755124</v>
+        <v>0.3466771652487887</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2913230338726246</v>
+        <v>0.2887512155740596</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4178677879491109</v>
+        <v>0.4125559178717221</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>113580</v>
+        <v>131580</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>100707</v>
+        <v>118012</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>128758</v>
+        <v>147101</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3855160608353929</v>
+        <v>0.3919970250334819</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3418229491682889</v>
+        <v>0.3515762777590758</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4370345511664972</v>
+        <v>0.4382365184806213</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86529</v>
+        <v>95813</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>77133</v>
+        <v>85632</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>96150</v>
+        <v>106509</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5789463591121906</v>
+        <v>0.5638068972617357</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5160828732690587</v>
+        <v>0.5038942950843568</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.6433227763949034</v>
+        <v>0.6267418771424224</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>94509</v>
+        <v>108273</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>84502</v>
+        <v>97355</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>102871</v>
+        <v>117872</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6510740432448761</v>
+        <v>0.6533228347512113</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5821322120508897</v>
+        <v>0.5874440821282777</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.7086769661273759</v>
+        <v>0.7112487844259402</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>181038</v>
+        <v>204086</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>165860</v>
+        <v>188565</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>193911</v>
+        <v>217654</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6144839391646071</v>
+        <v>0.6080029749665181</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.562965448833503</v>
+        <v>0.5617634815193787</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6581770508317112</v>
+        <v>0.6484237222409244</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>149459</v>
+        <v>169940</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>145159</v>
+        <v>165726</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>294618</v>
+        <v>335666</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>47603</v>
+        <v>56029</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>38822</v>
+        <v>46836</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>56632</v>
+        <v>65642</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4418843677908274</v>
+        <v>0.4436083712883959</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3603708523609565</v>
+        <v>0.370821937454814</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5256966820339218</v>
+        <v>0.5197221614528056</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>37194</v>
+        <v>42478</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>29610</v>
+        <v>34500</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>46032</v>
+        <v>51381</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3491576224419711</v>
+        <v>0.3385671070738551</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2779620716403925</v>
+        <v>0.2749777731278998</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.432118672309483</v>
+        <v>0.4095257275082025</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>84798</v>
+        <v>98507</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>73570</v>
+        <v>86021</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>96938</v>
+        <v>111563</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3957809208434637</v>
+        <v>0.3912626172542592</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3433753506646349</v>
+        <v>0.34166752270369</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4524420329325499</v>
+        <v>0.443120028879644</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>60125</v>
+        <v>70274</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>51096</v>
+        <v>60661</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>68906</v>
+        <v>79467</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5581156322091726</v>
+        <v>0.5563916287116041</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4743033179660782</v>
+        <v>0.4802778385471944</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6396291476390435</v>
+        <v>0.629178062545186</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>69332</v>
+        <v>82987</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>60494</v>
+        <v>74084</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>76916</v>
+        <v>90965</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6508423775580289</v>
+        <v>0.6614328929261449</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.567881327690517</v>
+        <v>0.5904742724917973</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7220379283596073</v>
+        <v>0.7250222268721001</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>129456</v>
+        <v>153260</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>117316</v>
+        <v>140204</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>140684</v>
+        <v>165746</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6042190791565363</v>
+        <v>0.6087373827457409</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5475579670674501</v>
+        <v>0.556879971120356</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6566246493353651</v>
+        <v>0.6583324772963101</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>107728</v>
+        <v>126303</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>106526</v>
+        <v>125465</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>214254</v>
+        <v>251767</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>28839</v>
+        <v>35952</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>22749</v>
+        <v>28375</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>35181</v>
+        <v>43822</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4588541715231488</v>
+        <v>0.4313257746723418</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3619560649182043</v>
+        <v>0.340420207789841</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.559774681843234</v>
+        <v>0.5257369553825281</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>15582</v>
+        <v>19249</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>10399</v>
+        <v>13675</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>21475</v>
+        <v>25951</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3044543246009532</v>
+        <v>0.3111359678882574</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2031880424417564</v>
+        <v>0.2210397256901133</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4195980529919181</v>
+        <v>0.4194613714879256</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>44420</v>
+        <v>55201</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>36469</v>
+        <v>45770</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>54044</v>
+        <v>65016</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3895543770902994</v>
+        <v>0.3801221558702025</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3198243149175339</v>
+        <v>0.3151756850611297</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4739499992583395</v>
+        <v>0.4477067314584152</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>34010</v>
+        <v>47401</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>27668</v>
+        <v>39531</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>40100</v>
+        <v>54978</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5411458284768512</v>
+        <v>0.5686742253276582</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4402253181567661</v>
+        <v>0.4742630446174708</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6380439350817958</v>
+        <v>0.6595797922101588</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>35598</v>
+        <v>42618</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>29705</v>
+        <v>35916</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>40781</v>
+        <v>48192</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6955456753990468</v>
+        <v>0.6888640321117426</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5804019470080819</v>
+        <v>0.5805386285120744</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7968119575582436</v>
+        <v>0.7789602743098866</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>69608</v>
+        <v>90019</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>59984</v>
+        <v>80204</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>77559</v>
+        <v>99450</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6104456229097005</v>
+        <v>0.6198778441297975</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.5260500007416605</v>
+        <v>0.5522932685415849</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6801756850824661</v>
+        <v>0.6848243149388702</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>62849</v>
+        <v>83353</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>51180</v>
+        <v>61867</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>114028</v>
+        <v>145220</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>234867</v>
+        <v>281127</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>217008</v>
+        <v>259556</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>254494</v>
+        <v>301437</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4528408337491344</v>
+        <v>0.449133584507334</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4184086793413084</v>
+        <v>0.4146723033744146</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4906835230739187</v>
+        <v>0.4815810802932842</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>168167</v>
+        <v>195609</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>151917</v>
+        <v>176708</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>185673</v>
+        <v>214617</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3496595783211826</v>
+        <v>0.3431505511685058</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.315872675388333</v>
+        <v>0.3099932966444192</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3860583987359593</v>
+        <v>0.376495428212155</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>583</v>
+        <v>692</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>403034</v>
+        <v>476736</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>376205</v>
+        <v>450598</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>428637</v>
+        <v>507236</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4031963428714455</v>
+        <v>0.3986185762010701</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3763562250721808</v>
+        <v>0.3767637976743126</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.4288093517483217</v>
+        <v>0.4241210042793997</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>403</v>
+        <v>489</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>283785</v>
+        <v>344804</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>264158</v>
+        <v>324494</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>301644</v>
+        <v>366375</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5471591662508656</v>
+        <v>0.550866415492666</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5093164769260814</v>
+        <v>0.5184189197067158</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5815913206586916</v>
+        <v>0.5853276966255855</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>466</v>
+        <v>559</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>312778</v>
+        <v>374430</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>295272</v>
+        <v>355422</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>329028</v>
+        <v>393331</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6503404216788174</v>
+        <v>0.6568494488314942</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6139416012640414</v>
+        <v>0.623504571787845</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.6841273246116671</v>
+        <v>0.6900067033555808</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>869</v>
+        <v>1048</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>596563</v>
+        <v>719234</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>570960</v>
+        <v>688734</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>623392</v>
+        <v>745372</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5968036571285545</v>
+        <v>0.60138142379893</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.5711906482516784</v>
+        <v>0.5758789957206003</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6236437749278194</v>
+        <v>0.6232362023256879</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>736</v>
+        <v>888</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>518652</v>
+        <v>625931</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>716</v>
+        <v>852</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>480945</v>
+        <v>570039</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1452</v>
+        <v>1740</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>999597</v>
+        <v>1195970</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3363,67 +3363,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>23189</v>
+        <v>24241</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>16931</v>
+        <v>17740</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>28891</v>
+        <v>29943</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5459295882772127</v>
+        <v>0.5358208912282538</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3985830930053235</v>
+        <v>0.392131233274489</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6801482728894859</v>
+        <v>0.6618453899673387</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>8012</v>
+        <v>9900</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4285</v>
+        <v>5630</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>12103</v>
+        <v>14390</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2580489833353501</v>
+        <v>0.2943608081301614</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1380169353152618</v>
+        <v>0.1674111231796891</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3898184038688926</v>
+        <v>0.4278837087047926</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>31201</v>
+        <v>34141</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>23491</v>
+        <v>25844</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>38841</v>
+        <v>42147</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4243666252087583</v>
+        <v>0.432861654465589</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3194993429234006</v>
+        <v>0.3276742373652464</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5282754667571453</v>
+        <v>0.5343695621706472</v>
       </c>
     </row>
     <row r="5">
@@ -3434,67 +3434,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>19288</v>
+        <v>21000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13586</v>
+        <v>15298</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>25546</v>
+        <v>27501</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4540704117227873</v>
+        <v>0.4641791087717462</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3198517271105141</v>
+        <v>0.338154610032661</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6014169069946765</v>
+        <v>0.6078687667255108</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>23035</v>
+        <v>23731</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>18944</v>
+        <v>19241</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>26762</v>
+        <v>28001</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7419510166646499</v>
+        <v>0.7056391918698386</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6101815961311072</v>
+        <v>0.5721162912952074</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.861983064684738</v>
+        <v>0.832588876820311</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>42323</v>
+        <v>44731</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>34683</v>
+        <v>36725</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>50033</v>
+        <v>53028</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5756333747912414</v>
+        <v>0.5671383455344108</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4717245332428546</v>
+        <v>0.4656304378293528</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.680500657076599</v>
+        <v>0.6723257626347535</v>
       </c>
     </row>
     <row r="6">
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>42477</v>
+        <v>45241</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3526,16 +3526,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>31047</v>
+        <v>33631</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3547,16 +3547,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>73524</v>
+        <v>78872</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3580,67 +3580,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>35059</v>
+        <v>36305</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>26893</v>
+        <v>27655</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>46014</v>
+        <v>46462</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3821486638094868</v>
+        <v>0.3788835616678229</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2931408455828541</v>
+        <v>0.288607209675715</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5015572031463227</v>
+        <v>0.484880495143524</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>20629</v>
+        <v>21452</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14660</v>
+        <v>15534</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>27445</v>
+        <v>28624</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3110845210750064</v>
+        <v>0.3021247620682313</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.221077222718526</v>
+        <v>0.2187833201185154</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4138685229087397</v>
+        <v>0.4031316324402022</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>55688</v>
+        <v>57756</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>44462</v>
+        <v>47331</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>68024</v>
+        <v>70363</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3523333570703633</v>
+        <v>0.3462138190625281</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2813042987058347</v>
+        <v>0.2837180313893994</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4303842724623547</v>
+        <v>0.4217829464640741</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>56683</v>
+        <v>59516</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>45728</v>
+        <v>49359</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>64849</v>
+        <v>68166</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6178513361905131</v>
+        <v>0.6211164383321772</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4984427968536773</v>
+        <v>0.515119504856476</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7068591544171455</v>
+        <v>0.7113927903242849</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>45684</v>
+        <v>49551</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>38868</v>
+        <v>42379</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>51653</v>
+        <v>55469</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6889154789249935</v>
+        <v>0.6978752379317688</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5861314770912611</v>
+        <v>0.5968683675597976</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.7789227772814741</v>
+        <v>0.7812166798814842</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>102367</v>
+        <v>109067</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>90031</v>
+        <v>96460</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>113593</v>
+        <v>119492</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6476666429296368</v>
+        <v>0.6537861809374718</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5696157275376454</v>
+        <v>0.5782170535359258</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7186957012941652</v>
+        <v>0.7162819686106005</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>91742</v>
+        <v>95821</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>66313</v>
+        <v>71003</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>158055</v>
+        <v>166823</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3797,67 +3797,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>43873</v>
+        <v>47062</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>34076</v>
+        <v>38242</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>52826</v>
+        <v>55858</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4364608613826682</v>
+        <v>0.4434953044649755</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3389979093405031</v>
+        <v>0.3603735446152762</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5255257951168506</v>
+        <v>0.5263845328246231</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>21588</v>
+        <v>23402</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>15216</v>
+        <v>17057</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>27925</v>
+        <v>30332</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2780196482932689</v>
+        <v>0.2892629616967015</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1959563128245243</v>
+        <v>0.2108382093821911</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3596326594295881</v>
+        <v>0.3749196217870289</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>65461</v>
+        <v>70465</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>55333</v>
+        <v>58511</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>76573</v>
+        <v>82770</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3674097723725495</v>
+        <v>0.3767763985375625</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3105680788426949</v>
+        <v>0.3128619022225714</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4297817810211579</v>
+        <v>0.4425724458956188</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56647</v>
+        <v>59055</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>47694</v>
+        <v>50259</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>66444</v>
+        <v>67875</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5635391386173318</v>
+        <v>0.5565046955350245</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4744742048831493</v>
+        <v>0.4736154671753771</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6610020906594968</v>
+        <v>0.6396264553847238</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>56060</v>
+        <v>57500</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>49723</v>
+        <v>50570</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>62432</v>
+        <v>63845</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7219803517067308</v>
+        <v>0.7107370383032984</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6403673405704118</v>
+        <v>0.625080378212971</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8040436871754757</v>
+        <v>0.7891617906178087</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>112707</v>
+        <v>116555</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>101595</v>
+        <v>104250</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>122835</v>
+        <v>128509</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6325902276274504</v>
+        <v>0.6232236014624375</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5702182189788421</v>
+        <v>0.5574275541043817</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6894319211573051</v>
+        <v>0.6871380977774288</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>100520</v>
+        <v>106117</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>77648</v>
+        <v>80902</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>178168</v>
+        <v>187020</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4014,67 +4014,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>17068</v>
+        <v>17526</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>11574</v>
+        <v>12407</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>23434</v>
+        <v>24180</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2986164430726855</v>
+        <v>0.2954312342944225</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2024876261349445</v>
+        <v>0.2091379466278857</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4100011220195751</v>
+        <v>0.4075876680634968</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>13006</v>
+        <v>13881</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>8390</v>
+        <v>9678</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>17617</v>
+        <v>19477</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2574717904838912</v>
+        <v>0.2648637045955468</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1660917665239523</v>
+        <v>0.1846608010706891</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3487673199304672</v>
+        <v>0.3716455733394739</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>30074</v>
+        <v>31407</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>22972</v>
+        <v>24319</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>38074</v>
+        <v>39725</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.279313538987389</v>
+        <v>0.281093651543366</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2133491450985646</v>
+        <v>0.2176564264330454</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3536163630876992</v>
+        <v>0.355536243555845</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>40089</v>
+        <v>41799</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>33723</v>
+        <v>35145</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>45583</v>
+        <v>46918</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7013835569273144</v>
+        <v>0.7045687657055776</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5899988779804247</v>
+        <v>0.5924123319365032</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7975123738650554</v>
+        <v>0.7908620533721142</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>37507</v>
+        <v>38527</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>32896</v>
+        <v>32931</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>42123</v>
+        <v>42730</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7425282095161089</v>
+        <v>0.7351362954044532</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6512326800695331</v>
+        <v>0.6283544266605264</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8339082334760477</v>
+        <v>0.8153391989293108</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>77597</v>
+        <v>80326</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>69597</v>
+        <v>72008</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>84699</v>
+        <v>87414</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7206864610126108</v>
+        <v>0.718906348456634</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6463836369123011</v>
+        <v>0.6444637564441551</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7866508549014354</v>
+        <v>0.7823435735669546</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>57157</v>
+        <v>59325</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>50513</v>
+        <v>52408</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>107671</v>
+        <v>111733</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>119190</v>
+        <v>125135</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>103629</v>
+        <v>109459</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>136310</v>
+        <v>140366</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4083289102848109</v>
+        <v>0.4082653181670117</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3550210878770767</v>
+        <v>0.3571205124323846</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4669820706482208</v>
+        <v>0.4579566635104974</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>63234</v>
+        <v>68634</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>51321</v>
+        <v>57453</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>74598</v>
+        <v>80378</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2803903762062169</v>
+        <v>0.2884474664607529</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2275668005661554</v>
+        <v>0.2414566191146476</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.330782587027325</v>
+        <v>0.3378011960510188</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>182423</v>
+        <v>193769</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>163966</v>
+        <v>173547</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>202600</v>
+        <v>213198</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.3525656960884628</v>
+        <v>0.3559004558150249</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3168929205289492</v>
+        <v>0.3187574239914105</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3915598109354776</v>
+        <v>0.3915855991106291</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>172706</v>
+        <v>181369</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>155586</v>
+        <v>166138</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>188267</v>
+        <v>197045</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5916710897151892</v>
+        <v>0.5917346818329884</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5330179293517792</v>
+        <v>0.5420433364895024</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6449789121229234</v>
+        <v>0.6428794875676154</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>162287</v>
+        <v>169310</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>150923</v>
+        <v>157566</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>174200</v>
+        <v>180491</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7196096237937831</v>
+        <v>0.7115525335392471</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.669217412972675</v>
+        <v>0.6621988039489811</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.7724331994338446</v>
+        <v>0.7585433808853519</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>334994</v>
+        <v>350679</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>314817</v>
+        <v>331250</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>353451</v>
+        <v>370901</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.6474343039115371</v>
+        <v>0.6440995441849749</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6084401890645219</v>
+        <v>0.6084144008893708</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6831070794710508</v>
+        <v>0.6812425760085893</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>291896</v>
+        <v>306504</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>225521</v>
+        <v>237944</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>517417</v>
+        <v>544448</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
